--- a/Documents/microcontrolador_precos.xlsx
+++ b/Documents/microcontrolador_precos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diogo\Documents\Projeto FINOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diogo\Documents\GitHub\DRINKO\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FD8709-4AF4-4417-956E-B22DAAABB008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E238B4A8-0486-4AEA-8CF8-0505B6FBDD2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="156" windowWidth="23040" windowHeight="12204" xr2:uid="{70A57D92-16A9-410E-AE88-7C626E365A8B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{70A57D92-16A9-410E-AE88-7C626E365A8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="73">
   <si>
     <t>board</t>
   </si>
@@ -1079,6 +1079,9 @@
       <c r="F29" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="G29" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="H29" t="s">
         <v>55</v>
       </c>
@@ -1096,6 +1099,9 @@
       <c r="F30" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="G30" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="H30" t="s">
         <v>57</v>
       </c>
@@ -1113,6 +1119,9 @@
       <c r="F31" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="G31" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="H31" t="s">
         <v>59</v>
       </c>
@@ -1130,6 +1139,9 @@
       <c r="F32" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="G32" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="H32" t="s">
         <v>61</v>
       </c>
@@ -1147,6 +1159,9 @@
       <c r="F33" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="G33" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="H33" t="s">
         <v>63</v>
       </c>
@@ -1164,6 +1179,9 @@
       <c r="F34" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="G34" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="H34" t="s">
         <v>65</v>
       </c>
@@ -1181,6 +1199,9 @@
       <c r="F35" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="G35" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="H35" t="s">
         <v>69</v>
       </c>
@@ -1198,6 +1219,9 @@
       <c r="F36" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="G36" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="H36" t="s">
         <v>70</v>
       </c>
@@ -1213,6 +1237,9 @@
     </row>
     <row r="37" spans="6:11" x14ac:dyDescent="0.3">
       <c r="F37" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H37" t="s">

--- a/Documents/microcontrolador_precos.xlsx
+++ b/Documents/microcontrolador_precos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diogo\Documents\GitHub\DRINKO\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E238B4A8-0486-4AEA-8CF8-0505B6FBDD2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04822758-6878-407D-A21D-DDEDCAC44DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{70A57D92-16A9-410E-AE88-7C626E365A8B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="96">
   <si>
     <t>board</t>
   </si>
@@ -255,6 +255,75 @@
   </si>
   <si>
     <t>https://pt.aliexpress.com/item/1005004336218242.html?spm=a2g0o.cart.0.0.188c7f06bKYqjx&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%202.99%21EUR%202.99%21%21EUR%202.99%21%21%21%40211b80f717550322996453403e26a5%2112000028806929716%21ct%21PT%216241319494%21%211%210&amp;gatewayAdapt=glo2bra</t>
+  </si>
+  <si>
+    <t>solda refrescante</t>
+  </si>
+  <si>
+    <t>16g</t>
+  </si>
+  <si>
+    <t>https://pt.aliexpress.com/item/1005007822631286.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%205.87%21EUR%202.93%21%21EUR%202.93%21%21%21%40211b431017613423690378299ec26b%2112000042332257561%21ct%21PT%216241319494%21%211%210&amp;gatewayAdapt=glo2bra</t>
+  </si>
+  <si>
+    <t>https://pt.aliexpress.com/item/1005009135360961.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%209.91%21EUR%204.45%21%21EUR%204.45%21%21%21%40211b431017613423690378299ec26b%2112000048042882601%21ct%21PT%216241319494%21%216%210&amp;gatewayAdapt=glo2bra</t>
+  </si>
+  <si>
+    <t>hx711 load cell</t>
+  </si>
+  <si>
+    <t>resistencias</t>
+  </si>
+  <si>
+    <t>https://pt.aliexpress.com/item/1005006863902202.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%208.01%21EUR%204.01%21%21EUR%204.01%21%21%21%40211b431017613423690378299ec26b%2112000051093471553%21ct%21PT%216241319494%21%211%210&amp;gatewayAdapt=glo2bra</t>
+  </si>
+  <si>
+    <t>https://pt.aliexpress.com/item/1005008829380291.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%202.37%21EUR%202.37%21%21EUR%202.37%21%21%21%40211b431017613423690378299ec26b%2112000046856831457%21ct%21PT%216241319494%21%211%210&amp;pdp_ext_f=%7B%22cart2PdpParams%22%3A%7B%22pdpBusinessMode%22%3A%22retail%22%7D%7D&amp;gatewayAdapt=glo2bra</t>
+  </si>
+  <si>
+    <t>mosfet 2N7000</t>
+  </si>
+  <si>
+    <t>fio solda</t>
+  </si>
+  <si>
+    <t>https://pt.aliexpress.com/item/1005006859440740.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%209.62%21EUR%204.33%21%21EUR%204.33%21%21%21%40211b431017613423690378299ec26b%2112000046627617708%21ct%21PT%216241319494%21%211%210&amp;gatewayAdapt=glo2bra</t>
+  </si>
+  <si>
+    <t>18650 shield</t>
+  </si>
+  <si>
+    <t>https://pt.aliexpress.com/item/1005007581124399.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%201.98%21EUR%201.98%21%21EUR%201.98%21%21%21%40211b431017613423690378299ec26b%2112000041384880223%21ct%21PT%216241319494%21%2112%210&amp;gatewayAdapt=glo2bra</t>
+  </si>
+  <si>
+    <t>https://pt.aliexpress.com/item/1005007671225942.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%2024.63%21EUR%2024.63%21%21EUR%2024.63%21%21%21%40211b431017613423690378299ec26b%2112000042934077717%21ct%21PT%216241319494%21%211%210&amp;gatewayAdapt=glo2bra</t>
+  </si>
+  <si>
+    <t>esp32</t>
+  </si>
+  <si>
+    <t>limpeza solda</t>
+  </si>
+  <si>
+    <t>https://pt.aliexpress.com/item/1005005623797293.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%208.06%21EUR%202.65%21%21EUR%202.65%21%21%21%40211b80e117613428754663876e7833%2112000033784605396%21ct%21PT%216241319494%21%211%210&amp;gatewayAdapt=glo2bra</t>
+  </si>
+  <si>
+    <t>https://pt.aliexpress.com/item/32973259342.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%201.65%21EUR%201.65%21%21EUR%201.65%21%21%21%40211b80e117613428754663876e7833%2166651074293%21ct%21PT%216241319494%21%211%210&amp;pdp_ext_f=%7B%22cart2PdpParams%22%3A%7B%22pdpBusinessMode%22%3A%22retail%22%7D%7D&amp;gatewayAdapt=glo2bra</t>
+  </si>
+  <si>
+    <t>capacitor 100nf</t>
+  </si>
+  <si>
+    <t>https://pt.aliexpress.com/item/1005006330415728.html?spm=a2g0o.order_list.order_list_main.5.21efcaa4mUaNB9&amp;gatewayAdapt=glo2bra</t>
+  </si>
+  <si>
+    <t>micro usb</t>
+  </si>
+  <si>
+    <t>breadboard</t>
+  </si>
+  <si>
+    <t>https://pt.aliexpress.com/item/1005009337105438.html?spm=a2g0o.order_list.order_list_main.10.21efcaa4mUaNB9&amp;gatewayAdapt=glo2bra</t>
   </si>
 </sst>
 </file>
@@ -644,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E5EEACA-D918-4AB7-BE98-0C8D09A79DB9}">
-  <dimension ref="F5:P39"/>
+  <dimension ref="F5:P51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="8" max="9" width="22.88671875" bestFit="1" customWidth="1"/>
@@ -1255,10 +1324,158 @@
         <v>72</v>
       </c>
     </row>
+    <row r="38" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="H38" t="s">
+        <v>73</v>
+      </c>
+      <c r="I38" t="s">
+        <v>74</v>
+      </c>
+      <c r="J38" s="1">
+        <v>2.93</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
     <row r="39" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="H39" t="s">
+        <v>77</v>
+      </c>
+      <c r="I39">
+        <v>6</v>
+      </c>
       <c r="J39" s="1">
-        <f>SUM(J6:J37)</f>
-        <v>183.75000000000006</v>
+        <v>26.7</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="H40" t="s">
+        <v>78</v>
+      </c>
+      <c r="I40">
+        <v>600</v>
+      </c>
+      <c r="J40" s="1">
+        <v>4.01</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="H41" t="s">
+        <v>81</v>
+      </c>
+      <c r="I41">
+        <v>50</v>
+      </c>
+      <c r="J41" s="1">
+        <v>2.37</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="H42" t="s">
+        <v>82</v>
+      </c>
+      <c r="J42" s="1">
+        <v>4.33</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="H43" t="s">
+        <v>84</v>
+      </c>
+      <c r="I43">
+        <v>12</v>
+      </c>
+      <c r="J43" s="1">
+        <v>23.76</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="H44" t="s">
+        <v>87</v>
+      </c>
+      <c r="I44">
+        <v>5</v>
+      </c>
+      <c r="J44" s="1">
+        <v>24.63</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="H45" t="s">
+        <v>88</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45" s="1">
+        <v>2.65</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="H46" t="s">
+        <v>91</v>
+      </c>
+      <c r="J46" s="1">
+        <v>1.65</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="H47" t="s">
+        <v>93</v>
+      </c>
+      <c r="I47">
+        <v>2</v>
+      </c>
+      <c r="J47" s="1">
+        <v>2.62</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="H48" t="s">
+        <v>94</v>
+      </c>
+      <c r="I48">
+        <v>6</v>
+      </c>
+      <c r="J48" s="1">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J51" s="1">
+        <f>SUM(J6:J48)</f>
+        <v>289.36</v>
       </c>
     </row>
   </sheetData>
@@ -1291,9 +1508,20 @@
     <hyperlink ref="K35" r:id="rId26" display="https://pt.aliexpress.com/item/1005003252824475.html?spm=a2g0o.cart.0.0.188c7f06bKYqjx&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%204.37%21EUR%204.09%21%21EUR%204.09%21%21%21%40211b80f717550322996453403e26a5%2112000024867532534%21ct%21PT%216241319494%21%211%210&amp;gatewayAdapt=glo2bra" xr:uid="{77BD1532-CBEA-4F71-9215-0DDF51B19D2A}"/>
     <hyperlink ref="K36" r:id="rId27" display="https://pt.aliexpress.com/item/1005004336218242.html?spm=a2g0o.cart.0.0.188c7f06bKYqjx&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%203.02%21EUR%203.02%21%21EUR%203.02%21%21%21%40211b80f717550322996453403e26a5%2112000028806929674%21ct%21PT%216241319494%21%211%210&amp;gatewayAdapt=glo2bra" xr:uid="{EFF4DC99-4B5B-4800-B40B-A54E6C800099}"/>
     <hyperlink ref="K37" r:id="rId28" display="https://pt.aliexpress.com/item/1005004336218242.html?spm=a2g0o.cart.0.0.188c7f06bKYqjx&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%202.99%21EUR%202.99%21%21EUR%202.99%21%21%21%40211b80f717550322996453403e26a5%2112000028806929716%21ct%21PT%216241319494%21%211%210&amp;gatewayAdapt=glo2bra" xr:uid="{E7573F72-DEBF-4FC5-948B-CD6929C5561C}"/>
+    <hyperlink ref="K38" r:id="rId29" display="https://pt.aliexpress.com/item/1005007822631286.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%205.87%21EUR%202.93%21%21EUR%202.93%21%21%21%40211b431017613423690378299ec26b%2112000042332257561%21ct%21PT%216241319494%21%211%210&amp;gatewayAdapt=glo2bra" xr:uid="{051E5C13-6AAF-4AE8-9892-90116C0B303C}"/>
+    <hyperlink ref="K39" r:id="rId30" display="https://pt.aliexpress.com/item/1005009135360961.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%209.91%21EUR%204.45%21%21EUR%204.45%21%21%21%40211b431017613423690378299ec26b%2112000048042882601%21ct%21PT%216241319494%21%216%210&amp;gatewayAdapt=glo2bra" xr:uid="{9421C827-E289-403F-8AD3-98E5DCF76B34}"/>
+    <hyperlink ref="K40" r:id="rId31" display="https://pt.aliexpress.com/item/1005006863902202.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%208.01%21EUR%204.01%21%21EUR%204.01%21%21%21%40211b431017613423690378299ec26b%2112000051093471553%21ct%21PT%216241319494%21%211%210&amp;gatewayAdapt=glo2bra" xr:uid="{08817F36-F942-4F60-9F16-2A48D70E3992}"/>
+    <hyperlink ref="K41" r:id="rId32" display="https://pt.aliexpress.com/item/1005008829380291.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%202.37%21EUR%202.37%21%21EUR%202.37%21%21%21%40211b431017613423690378299ec26b%2112000046856831457%21ct%21PT%216241319494%21%211%210&amp;pdp_ext_f=%7B%22cart2PdpParams%22%3A%7B%22pdpBusinessMode%22%3A%22retail%22%7D%7D&amp;gatewayAdapt=glo2bra" xr:uid="{E8E6BD00-2728-45BC-8688-E84054845AAE}"/>
+    <hyperlink ref="K42" r:id="rId33" display="https://pt.aliexpress.com/item/1005006859440740.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%209.62%21EUR%204.33%21%21EUR%204.33%21%21%21%40211b431017613423690378299ec26b%2112000046627617708%21ct%21PT%216241319494%21%211%210&amp;gatewayAdapt=glo2bra" xr:uid="{4805FAEA-9A62-4624-ADD3-6E0D29AD3507}"/>
+    <hyperlink ref="K43" r:id="rId34" display="https://pt.aliexpress.com/item/1005007581124399.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%201.98%21EUR%201.98%21%21EUR%201.98%21%21%21%40211b431017613423690378299ec26b%2112000041384880223%21ct%21PT%216241319494%21%2112%210&amp;gatewayAdapt=glo2bra" xr:uid="{9C37EA9E-5ECB-4EBD-92ED-008A385F0B5B}"/>
+    <hyperlink ref="K44" r:id="rId35" display="https://pt.aliexpress.com/item/1005007671225942.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%2024.63%21EUR%2024.63%21%21EUR%2024.63%21%21%21%40211b431017613423690378299ec26b%2112000042934077717%21ct%21PT%216241319494%21%211%210&amp;gatewayAdapt=glo2bra" xr:uid="{FAC15BA6-1DEF-4CD0-8A63-29522F694C3B}"/>
+    <hyperlink ref="K45" r:id="rId36" display="https://pt.aliexpress.com/item/1005005623797293.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%208.06%21EUR%202.65%21%21EUR%202.65%21%21%21%40211b80e117613428754663876e7833%2112000033784605396%21ct%21PT%216241319494%21%211%210&amp;gatewayAdapt=glo2bra" xr:uid="{EFBA3D66-E136-4AB5-B20A-001F1EAA560D}"/>
+    <hyperlink ref="K46" r:id="rId37" display="https://pt.aliexpress.com/item/32973259342.html?spm=a2g0o.cart.0.0.49d87f06odsodV&amp;mp=1&amp;pdp_npi=5%40dis%21EUR%21EUR%201.65%21EUR%201.65%21%21EUR%201.65%21%21%21%40211b80e117613428754663876e7833%2166651074293%21ct%21PT%216241319494%21%211%210&amp;pdp_ext_f=%7B%22cart2PdpParams%22%3A%7B%22pdpBusinessMode%22%3A%22retail%22%7D%7D&amp;gatewayAdapt=glo2bra" xr:uid="{2BA3958A-BFAB-4F6C-96C9-98D4678D300F}"/>
+    <hyperlink ref="K47" r:id="rId38" xr:uid="{31687172-1183-4189-946D-31EABAF561C3}"/>
+    <hyperlink ref="K48" r:id="rId39" xr:uid="{EBAF61A4-9B70-4CEF-976A-6284042EBD08}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId29"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId40"/>
 </worksheet>
 </file>
 

--- a/Documents/microcontrolador_precos.xlsx
+++ b/Documents/microcontrolador_precos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Diogo\Documents\GitHub\DRINKO\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04822758-6878-407D-A21D-DDEDCAC44DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61571C4-F2C0-4E21-9BD1-2B46FFA7B982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{70A57D92-16A9-410E-AE88-7C626E365A8B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="96">
   <si>
     <t>board</t>
   </si>
@@ -1325,6 +1325,9 @@
       </c>
     </row>
     <row r="38" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F38" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="H38" t="s">
         <v>73</v>
       </c>
@@ -1339,6 +1342,12 @@
       </c>
     </row>
     <row r="39" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="H39" t="s">
         <v>77</v>
       </c>
@@ -1353,6 +1362,12 @@
       </c>
     </row>
     <row r="40" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="H40" t="s">
         <v>78</v>
       </c>
@@ -1367,6 +1382,12 @@
       </c>
     </row>
     <row r="41" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F41" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" t="s">
+        <v>29</v>
+      </c>
       <c r="H41" t="s">
         <v>81</v>
       </c>
@@ -1381,6 +1402,12 @@
       </c>
     </row>
     <row r="42" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G42" t="s">
+        <v>29</v>
+      </c>
       <c r="H42" t="s">
         <v>82</v>
       </c>
@@ -1392,6 +1419,12 @@
       </c>
     </row>
     <row r="43" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G43" t="s">
+        <v>29</v>
+      </c>
       <c r="H43" t="s">
         <v>84</v>
       </c>
@@ -1406,6 +1439,12 @@
       </c>
     </row>
     <row r="44" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G44" t="s">
+        <v>29</v>
+      </c>
       <c r="H44" t="s">
         <v>87</v>
       </c>
@@ -1420,6 +1459,12 @@
       </c>
     </row>
     <row r="45" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F45" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G45" t="s">
+        <v>29</v>
+      </c>
       <c r="H45" t="s">
         <v>88</v>
       </c>
@@ -1434,6 +1479,12 @@
       </c>
     </row>
     <row r="46" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G46" t="s">
+        <v>29</v>
+      </c>
       <c r="H46" t="s">
         <v>91</v>
       </c>
@@ -1445,6 +1496,9 @@
       </c>
     </row>
     <row r="47" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F47" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="H47" t="s">
         <v>93</v>
       </c>
@@ -1459,6 +1513,9 @@
       </c>
     </row>
     <row r="48" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F48" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="H48" t="s">
         <v>94</v>
       </c>
